--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3452.55</v>
+        <v>3446.78</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>16821.93</v>
+        <v>16721.11</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10549.64</v>
+        <v>10406.21</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>22658.99</v>
+        <v>22350.92</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8873.209999999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>65088.11</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>27894.91</v>
+        <v>27721.96</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>25437.68</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7637.95</v>
+        <v>7690.68</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>66151.25</v>
+        <v>66607.96000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>27147.91</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>22138.31</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>22138.97</v>
+        <v>22080.42</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1379.63</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11955.05</v>
+        <v>11709.35</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9667.34</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12245.28</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>64448.86</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6015.23</v>
+        <v>6002.14</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1278.24</v>
+        <v>1275.46</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1278.24</v>
+        <v>1275.67</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>1078629-11-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>27231.85</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1078629-11-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>22206.75</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="14">
@@ -1790,6 +1790,494 @@
       </c>
       <c r="M22" s="2" t="n">
         <v>1275.67</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1488-903-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>208859.42</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1488-904-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>83035.34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3517-127-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.180.700-2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.336.696-0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>8099.82</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1658-2266-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TRANSPORTES ALV-BAACK SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>77.314.274-2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>16359.18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2546-726-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>71178.27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1523-1816-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.602.236-9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>16.995.419-4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>249028.09</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1658-2410-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TRANSPORTES ALV-BAACK SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>77.314.274-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>41604.95</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>660-24-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.834.000-7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Patricio Osvaldo</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.845.503-1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>79190.19</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057387-333-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>66607.96000000001</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="12">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>4057-471-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.181.100-k</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>27231.85</v>
+        <v>22080.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4057-471-CM26</t>
+          <t>748-51-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.181.100-k</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>22080.42</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>748-51-CM26</t>
+          <t>2546-635-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1375.98</v>
+        <v>11709.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2546-635-CM26</t>
+          <t>1488-1054-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11709.35</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1488-1054-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9732.040000000001</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1523-1545-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12330.98</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>748-58-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.845.503-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>64308.63</v>
+        <v>6002.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>748-58-CM26</t>
+          <t>748-59-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PATRICIO OSVALDO</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6002.14</v>
+        <v>1275.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>748-59-CM26</t>
+          <t>4887-85-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.978.390-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PATRICIO OSVALDO</t>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.845.503-1</t>
+          <t>15.552.949-0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1275.46</v>
+        <v>1275.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4887-85-CM26</t>
+          <t>1488-903-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.978.390-5</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Region de la Araucania</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15.552.949-0</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1275.67</v>
+        <v>208859.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1488-903-CM26</t>
+          <t>1488-904-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>208859.42</v>
+        <v>83035.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1488-904-CM26</t>
+          <t>3517-127-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>83035.34</v>
+        <v>8099.82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3517-127-CM26</t>
+          <t>1658-2266-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>TRANSPORTES ALV-BAACK SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>77.314.274-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8099.82</v>
+        <v>16359.18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1658-2266-CM26</t>
+          <t>2546-726-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRANSPORTES ALV-BAACK SPA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.314.274-2</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>16359.18</v>
+        <v>71178.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2546-726-CM26</t>
+          <t>1523-1816-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>16.995.419-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>71178.27</v>
+        <v>249028.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1523-1816-CM26</t>
+          <t>1658-2410-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+          <t>TRANSPORTES ALV-BAACK SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16.995.419-4</t>
+          <t>77.314.274-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>249028.09</v>
+        <v>41604.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1658-2410-CM26</t>
+          <t>660-24-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>61.834.000-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TRANSPORTES ALV-BAACK SPA</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.314.274-2</t>
+          <t>76.845.503-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>41604.95</v>
+        <v>79190.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>660-24-CM26</t>
+          <t>2085-746-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.834.000-7</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Patricio Osvaldo</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.845.503-1</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,7 +2277,617 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>79190.19</v>
+        <v>19927.15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1075337-9749-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.602.222-9</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Transportes Luis Rifo y compañia limitada</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.114.087-6</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>64205.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1488-1234-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>46989.46</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1079659-376-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.980.860-6</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>14866.12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>748-77-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ALEMOSO SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.852.175-K</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>12593.45</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>748-79-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>7309.89</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>748-80-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ALEMOSO SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.852.175-K</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>4039.9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>748-81-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>2327.35</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>678-45-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.402.018-0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>21007.77</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>678-46-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.402.018-0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>15729.88</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3517-190-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.180.700-2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.336.696-0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>18282.18</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
@@ -1111,7 +1111,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +1969,11 @@
           <t>77.314.274-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2156,11 @@
           <t>77.314.274-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2526,11 @@
           <t>77.852.175-K</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2652,11 @@
           <t>77.852.175-K</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1488-545-CM26</t>
+          <t>1488-639-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>64684.58</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="8">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1488-639-CM26</t>
+          <t>1488-545-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>25279.97</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="10">
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>1078629-11-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>27231.85</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1078629-11-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,28 +1168,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>22206.75</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4057-471-CM26</t>
+          <t>748-51-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1209,17 +1213,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.181.100-k</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1233,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1248,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>22080.42</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>748-51-CM26</t>
+          <t>4057-471-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1270,17 +1274,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.181.100-k</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1294,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,7 +1309,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1375.98</v>
+        <v>22080.42</v>
       </c>
     </row>
     <row r="15">
@@ -1494,7 +1498,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>748-58-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1519,12 +1523,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1538,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.845.503-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1553,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>64308.63</v>
+        <v>6002.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>748-58-CM26</t>
+          <t>748-59-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1610,13 +1614,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6002.14</v>
+        <v>1275.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>748-59-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1641,12 +1645,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1660,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Patricio Osvaldo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.845.503-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,7 +1675,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1275.46</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="21">
@@ -2315,7 +2319,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2376,7 +2380,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2478,7 +2482,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>748-77-CM26</t>
+          <t>748-81-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2518,32 +2522,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ALEMOSO SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.852.175-K</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12593.45</v>
+        <v>2327.35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>748-79-CM26</t>
+          <t>748-80-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2583,28 +2583,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>ALEMOSO SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>77.852.175-K</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7309.89</v>
+        <v>4039.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>748-80-CM26</t>
+          <t>748-79-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2624,7 +2628,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2644,32 +2648,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ALEMOSO SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.852.175-K</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4039.9</v>
+        <v>7309.89</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>748-81-CM26</t>
+          <t>748-77-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2709,28 +2709,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>ALEMOSO SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>77.852.175-K</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2327.35</v>
+        <v>12593.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>678-45-CM26</t>
+          <t>678-46-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2750,7 +2754,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2778,20 +2782,24 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>21007.77</v>
+        <v>15729.88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>678-46-CM26</t>
+          <t>678-45-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2811,7 +2819,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2839,14 +2847,18 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>15729.88</v>
+        <v>21007.77</v>
       </c>
     </row>
     <row r="40">
@@ -2908,6 +2920,376 @@
       </c>
       <c r="M40" s="2" t="n">
         <v>18282.18</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>960841-61-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.180.500-K</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>3655.49</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1200-241-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>35338.24</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1200-252-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ALEMOSO SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.852.175-K</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>8299.43</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1523-2401-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.602.236-9</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>15.552.949-0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>7699.87</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2547-249-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>6825.24</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2546-979-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>12284.76</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/araucania.xlsx
@@ -1148,7 +1148,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
